--- a/menu.xlsx
+++ b/menu.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/unmello/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/unmello/Documents/GitHub/Vozmogno_vce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3DF40EB-5106-2A43-B06F-F307EEB850F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2308313-BEFA-5048-9B99-BED1127EAAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="660" windowWidth="34560" windowHeight="19440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -819,7 +819,9 @@
       <c r="F2" s="7">
         <v>190</v>
       </c>
-      <c r="G2" s="4"/>
+      <c r="G2" s="4">
+        <v>5</v>
+      </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>

--- a/menu.xlsx
+++ b/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/unmello/Documents/GitHub/Vozmogno_vce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2308313-BEFA-5048-9B99-BED1127EAAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89110F67-3D69-4E40-A9CF-B5BE8B5ECC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -838,7 +838,9 @@
       <c r="F3" s="7">
         <v>160</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="4" spans="1:9" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
